--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CLAYPOLE 1.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CLAYPOLE 1.xlsx
@@ -308,803 +308,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>777240</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="3 Imagen" descr="uriel pantuso.jpeg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591801" y="2994661"/>
-          <a:ext cx="777239" cy="899159"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>853440</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="4 Imagen" descr="benja moreno.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10607040" y="10317480"/>
-          <a:ext cx="838200" cy="746760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>853440</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>762000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="5 Imagen" descr="leonel almiron.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10599420" y="12633960"/>
-          <a:ext cx="845820" cy="754380"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>853440</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="6 Imagen" descr="santiago hermosa.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="14157960"/>
-          <a:ext cx="853440" cy="822960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>800100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="7 Imagen" descr="isaias malfatti.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10599420" y="7955280"/>
-          <a:ext cx="830580" cy="891540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="8 Imagen" descr="PROFE LAUTY.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="15720060"/>
-          <a:ext cx="876300" cy="723900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>822960</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>838200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="9 Imagen" descr="DYLAN FERNANDEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="5501640"/>
-          <a:ext cx="822960" cy="838200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="10 Imagen" descr="ULISES MACHUCA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="8823960"/>
-          <a:ext cx="868680" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>853440</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>754380</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="11 Imagen" descr="ARIEL CONTHE.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="11864340"/>
-          <a:ext cx="853440" cy="754380"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>906780</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="12 Imagen" descr="PROFE SERGIO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="16436340"/>
-          <a:ext cx="906780" cy="792480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>822960</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="13 Imagen" descr="AGUSTIN LEDESMA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="3886200"/>
-          <a:ext cx="822960" cy="800100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>845820</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>815340</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="14 Imagen" descr="SERGIO JOEL GOMEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="4678680"/>
-          <a:ext cx="845820" cy="815340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>845820</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="15 Imagen" descr="AGUSTIN FERNANDEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="7155180"/>
-          <a:ext cx="845820" cy="845820"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>845820</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="16 Imagen" descr="DANIEL GROSSI.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="9578340"/>
-          <a:ext cx="845820" cy="739140"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>861060</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="17 Imagen" descr="LUCIANO CATRILAF.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="11064240"/>
-          <a:ext cx="861060" cy="807720"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="18 Imagen" descr="DYLAN PEREZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="14973300"/>
-          <a:ext cx="838200" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="19 Imagen" descr="FERNANDO IÑIGO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="13403580"/>
-          <a:ext cx="868680" cy="754380"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="20 Imagen" descr="DYLAN ROMERO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="6355080"/>
-          <a:ext cx="868680" cy="800100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
